--- a/data/trans_bre/IP18A05-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP18A05-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,53</t>
+          <t>0,0; 7,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,7</t>
+          <t>0,0; 27,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,44</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 6,95</t>
+          <t>-5,12; 5,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,0; 3,81</t>
+          <t>-27,91; 3,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,19; 363,12</t>
+          <t>-74,47; 258,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 1,13</t>
+          <t>-6,08; 1,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 0,0</t>
+          <t>-6,52; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,7</t>
+          <t>0,0; 23,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,49</t>
+          <t>0,0; 5,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 0,0</t>
+          <t>-5,19; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,96</t>
+          <t>0,0; 4,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 0,0</t>
+          <t>-12,58; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-45,65; 0,0</t>
+          <t>-46,76; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 3,44</t>
+          <t>-8,84; 3,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,69</t>
+          <t>-0,93; 3,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 2,07</t>
+          <t>-5,63; 2,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 4,02</t>
+          <t>-24,64; 4,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-92,48; 205,55</t>
+          <t>-91,77; 240,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1360,12 +1360,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,7</t>
+          <t>-3,32; 1,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,92</t>
+          <t>-1,46; 1,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 0,0</t>
+          <t>-21,56; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,85</t>
+          <t>-0,72; 0,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,55</t>
+          <t>-1,1; 0,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,87</t>
+          <t>-1,32; 0,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 2,44</t>
+          <t>-6,24; 2,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-76,8; 389,36</t>
+          <t>-81,27; 358,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-73,59; 98,6</t>
+          <t>-73,8; 82,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-65,93; 126,33</t>
+          <t>-67,66; 105,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-89,06; 125,86</t>
+          <t>-90,42; 142,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A05-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP18A05-Provincia-trans_bre.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,23</t>
+          <t>0,0; 7,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,23</t>
+          <t>0,0; 25,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 5,42</t>
+          <t>-5,17; 5,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,91; 3,73</t>
+          <t>-31,21; 4,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-74,47; 258,7</t>
+          <t>-74,56; 231,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 1,96</t>
+          <t>-6,1; 1,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 0,0</t>
+          <t>-5,52; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,34</t>
+          <t>0,0; 22,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,93</t>
+          <t>0,0; 8,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 0,0</t>
+          <t>-5,22; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>0,0; 3,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 0,0</t>
+          <t>-12,59; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-46,76; 0,0</t>
+          <t>-49,87; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 3,9</t>
+          <t>-8,5; 4,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 362,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,08</t>
+          <t>-0,84; 3,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 2,28</t>
+          <t>-5,93; 2,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-24,64; 4,21</t>
+          <t>-23,76; 3,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-91,77; 240,54</t>
+          <t>-89,97; 216,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1360,12 +1360,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 1,64</t>
+          <t>-3,31; 1,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,75</t>
+          <t>-1,59; 2,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 0,0</t>
+          <t>-18,44; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,85</t>
+          <t>-0,63; 0,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,54</t>
+          <t>-1,17; 0,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,81</t>
+          <t>-1,31; 0,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 2,35</t>
+          <t>-6,08; 2,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-81,27; 358,44</t>
+          <t>-80,02; 384,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-73,8; 82,69</t>
+          <t>-75,97; 103,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-67,66; 105,86</t>
+          <t>-68,33; 82,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-90,42; 142,83</t>
+          <t>-85,87; 135,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A05-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP18A05-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,4</t>
+          <t>5,19</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,28</t>
+          <t>0,0; 6,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,35</t>
+          <t>0,0; 24,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,85</t>
+          <t>-6,37</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-65,74%</t>
+          <t>-69,98%</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 5,14</t>
+          <t>-4,85; 6,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,21; 4,07</t>
+          <t>-33,04; 3,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-74,56; 231,79</t>
+          <t>-71,19; 363,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,45</t>
+          <t>6,99</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 1,1</t>
+          <t>-6,36; 1,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 0,0</t>
+          <t>-4,85; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,93</t>
+          <t>0,0; 21,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,22</t>
+          <t>0,0; 6,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 0,0</t>
+          <t>-5,27; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,9</t>
+          <t>0,0; 3,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-10,7</t>
+          <t>-10,42</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 0,0</t>
+          <t>-14,5; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-49,87; 0,0</t>
+          <t>-44,88; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 4,19</t>
+          <t>-8,65; 3,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 362,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-7,22</t>
+          <t>-6,52</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-67,13%</t>
+          <t>-60,09%</t>
         </is>
       </c>
     </row>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,02</t>
+          <t>-0,48; 2,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 2,38</t>
+          <t>-6,11; 2,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,76; 3,81</t>
+          <t>-22,07; 6,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-89,97; 216,19</t>
+          <t>-92,48; 205,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-3,54</t>
+          <t>-3,17</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1360,12 +1360,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 1,78</t>
+          <t>-3,29; 1,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,07</t>
+          <t>-1,66; 1,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 0,0</t>
+          <t>-15,97; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>-1,66</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-33,54%</t>
+          <t>-36,59%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,81</t>
+          <t>-0,66; 0,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,59</t>
+          <t>-1,15; 0,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,66</t>
+          <t>-1,32; 0,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 2,5</t>
+          <t>-7,05; 2,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-80,02; 384,51</t>
+          <t>-76,8; 389,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-75,97; 103,53</t>
+          <t>-73,59; 98,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-68,33; 82,77</t>
+          <t>-65,93; 126,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-85,87; 135,36</t>
+          <t>-90,42; 127,21</t>
         </is>
       </c>
     </row>
